--- a/Plates/nitrate_key.xlsx
+++ b/Plates/nitrate_key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaedonswanson/Desktop/School/MS/Research/Microplate/Plates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE509278-6547-4E44-A83B-63B6FE9E3273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9464C6-1B0C-1644-A740-946FD0B047EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17280" yWindow="660" windowWidth="17280" windowHeight="21680" activeTab="1" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="1" activeTab="5" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Format" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="74">
   <si>
     <t>A</t>
   </si>
@@ -127,27 +127,15 @@
     <t>elm-school_06012026</t>
   </si>
   <si>
-    <t>her-resi_06122026</t>
-  </si>
-  <si>
-    <t>adams-out_0612026</t>
-  </si>
-  <si>
     <t>elm-school_05222026</t>
   </si>
   <si>
-    <t>her-resi_05282026</t>
-  </si>
-  <si>
     <t>adams-in_06012026</t>
   </si>
   <si>
     <t>elm-school_06122026</t>
   </si>
   <si>
-    <t>her-out_05282026</t>
-  </si>
-  <si>
     <t>adams-in_06122026</t>
   </si>
   <si>
@@ -157,42 +145,21 @@
     <t>JUST_REAGENT</t>
   </si>
   <si>
-    <t>adams-mid_06122026</t>
-  </si>
-  <si>
     <t>gcp_06122026</t>
   </si>
   <si>
-    <t>elm-bridge_06011026</t>
-  </si>
-  <si>
     <t>ERROR</t>
   </si>
   <si>
     <t>elm-bridge_06122026</t>
   </si>
   <si>
-    <t>her-out_06122026</t>
-  </si>
-  <si>
     <t>elm-bridge_05222026</t>
   </si>
   <si>
-    <t>her-map_06122026</t>
-  </si>
-  <si>
-    <t>her-resi_06172026</t>
-  </si>
-  <si>
     <t>gcp_06172026</t>
   </si>
   <si>
-    <t>her-out_06172026</t>
-  </si>
-  <si>
-    <t>her-map_06172026</t>
-  </si>
-  <si>
     <t>elm-school_06172026</t>
   </si>
   <si>
@@ -202,30 +169,18 @@
     <t>adams-in_06172026</t>
   </si>
   <si>
-    <t>adams-mid_06172026</t>
-  </si>
-  <si>
     <t>adams-out_06172026</t>
   </si>
   <si>
-    <t>her-map_06192026</t>
-  </si>
-  <si>
     <t>heron-map_06172026</t>
   </si>
   <si>
-    <t>her-resi_06192026</t>
-  </si>
-  <si>
     <t>adams-mid-down_06172026</t>
   </si>
   <si>
     <t>heron-resi_06172026</t>
   </si>
   <si>
-    <t>her-out_06192026</t>
-  </si>
-  <si>
     <t>heron-out_06172026</t>
   </si>
   <si>
@@ -256,9 +211,6 @@
     <t>heron-out_05282026</t>
   </si>
   <si>
-    <t>adams-out_06012926</t>
-  </si>
-  <si>
     <t>heron-out_06122026</t>
   </si>
   <si>
@@ -268,9 +220,6 @@
     <t>adams-out_06122026</t>
   </si>
   <si>
-    <t>heron-map-06122026</t>
-  </si>
-  <si>
     <t>elm-bridge_06112026</t>
   </si>
   <si>
@@ -289,9 +238,6 @@
     <t>adams-mid-up_06212026</t>
   </si>
   <si>
-    <t>adams-mid-down-06212026</t>
-  </si>
-  <si>
     <t>adams-out_06212026</t>
   </si>
   <si>
@@ -305,6 +251,24 @@
   </si>
   <si>
     <t>heron-map_06212026</t>
+  </si>
+  <si>
+    <t>heron-map_06122026</t>
+  </si>
+  <si>
+    <t>heron-map_06192026</t>
+  </si>
+  <si>
+    <t>heron-resi_06192026</t>
+  </si>
+  <si>
+    <t>heron-out_06192026</t>
+  </si>
+  <si>
+    <t>adams-mid-down_06212026</t>
+  </si>
+  <si>
+    <t>elm-bridge_06012026</t>
   </si>
 </sst>
 </file>
@@ -346,11 +310,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -900,22 +865,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="E2:G2"/>
@@ -932,6 +881,22 @@
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="K8:M8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1005,7 +970,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1020,17 +985,17 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1045,17 +1010,17 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1070,17 +1035,17 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -1095,17 +1060,17 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -1120,17 +1085,17 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -1145,17 +1110,17 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -1170,18 +1135,274 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>35</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:M9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55F4A5C2-CC37-4DE5-8D3C-DCD54EC66921}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
@@ -1212,20 +1433,21 @@
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="E2:G2"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:G3"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="K3:M3"/>
-    <mergeCell ref="E2:G2"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55F4A5C2-CC37-4DE5-8D3C-DCD54EC66921}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F440DE84-DF99-4AAA-815E-10A80CB578E0}">
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1281,16 +1503,18 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+      <c r="K2" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
@@ -1304,14 +1528,18 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
+      <c r="K3" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
@@ -1325,14 +1553,18 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="H4" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+      <c r="K4" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
@@ -1346,14 +1578,18 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
@@ -1367,14 +1603,18 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
@@ -1388,14 +1628,18 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
@@ -1409,14 +1653,18 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
@@ -1434,10 +1682,14 @@
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="H9" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
@@ -1481,8 +1733,709 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F440DE84-DF99-4AAA-815E-10A80CB578E0}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{789EDA15-6520-4C56-8C16-6BF2362B08F7}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="19.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9D2C9A-CA68-4C73-8E9C-B2F3F39F8518}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9A2FE2-4864-4798-9335-55F3D4E7525C}">
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1533,23 +2486,21 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
@@ -1558,23 +2509,21 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
@@ -1583,23 +2532,21 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
@@ -1608,23 +2555,21 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
@@ -1633,23 +2578,21 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
@@ -1658,23 +2601,19 @@
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
@@ -1683,23 +2622,19 @@
         <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
@@ -1708,23 +2643,278 @@
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="1" t="s">
-        <v>68</v>
-      </c>
+      <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:M9"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF55D13E-4202-B24E-90AB-F581E60463A8}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
@@ -1763,13 +2953,12 @@
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="K3:M3"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{789EDA15-6520-4C56-8C16-6BF2362B08F7}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A762176-A398-AB4C-A136-6BF964D77C5A}">
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1825,18 +3014,16 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
@@ -1850,18 +3037,16 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
@@ -1875,18 +3060,14 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
@@ -1900,18 +3081,14 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
@@ -1925,18 +3102,14 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="1" t="s">
-        <v>63</v>
-      </c>
+      <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
@@ -1950,18 +3123,14 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
@@ -1975,18 +3144,14 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
@@ -2000,18 +3165,14 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="1" t="s">
-        <v>68</v>
-      </c>
+      <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
@@ -2050,1064 +3211,11 @@
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="K3:M3"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9D2C9A-CA68-4C73-8E9C-B2F3F39F8518}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B1">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <v>2</v>
-      </c>
-      <c r="D1">
-        <v>3</v>
-      </c>
-      <c r="E1">
-        <v>4</v>
-      </c>
-      <c r="F1">
-        <v>5</v>
-      </c>
-      <c r="G1">
-        <v>6</v>
-      </c>
-      <c r="H1">
-        <v>7</v>
-      </c>
-      <c r="I1">
-        <v>8</v>
-      </c>
-      <c r="J1">
-        <v>9</v>
-      </c>
-      <c r="K1">
-        <v>10</v>
-      </c>
-      <c r="L1">
-        <v>11</v>
-      </c>
-      <c r="M1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9A2FE2-4864-4798-9335-55F3D4E7525C}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B1">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <v>2</v>
-      </c>
-      <c r="D1">
-        <v>3</v>
-      </c>
-      <c r="E1">
-        <v>4</v>
-      </c>
-      <c r="F1">
-        <v>5</v>
-      </c>
-      <c r="G1">
-        <v>6</v>
-      </c>
-      <c r="H1">
-        <v>7</v>
-      </c>
-      <c r="I1">
-        <v>8</v>
-      </c>
-      <c r="J1">
-        <v>9</v>
-      </c>
-      <c r="K1">
-        <v>10</v>
-      </c>
-      <c r="L1">
-        <v>11</v>
-      </c>
-      <c r="M1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF55D13E-4202-B24E-90AB-F581E60463A8}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B1">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <v>2</v>
-      </c>
-      <c r="D1">
-        <v>3</v>
-      </c>
-      <c r="E1">
-        <v>4</v>
-      </c>
-      <c r="F1">
-        <v>5</v>
-      </c>
-      <c r="G1">
-        <v>6</v>
-      </c>
-      <c r="H1">
-        <v>7</v>
-      </c>
-      <c r="I1">
-        <v>8</v>
-      </c>
-      <c r="J1">
-        <v>9</v>
-      </c>
-      <c r="K1">
-        <v>10</v>
-      </c>
-      <c r="L1">
-        <v>11</v>
-      </c>
-      <c r="M1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A762176-A398-AB4C-A136-6BF964D77C5A}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B1">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <v>2</v>
-      </c>
-      <c r="D1">
-        <v>3</v>
-      </c>
-      <c r="E1">
-        <v>4</v>
-      </c>
-      <c r="F1">
-        <v>5</v>
-      </c>
-      <c r="G1">
-        <v>6</v>
-      </c>
-      <c r="H1">
-        <v>7</v>
-      </c>
-      <c r="I1">
-        <v>8</v>
-      </c>
-      <c r="J1">
-        <v>9</v>
-      </c>
-      <c r="K1">
-        <v>10</v>
-      </c>
-      <c r="L1">
-        <v>11</v>
-      </c>
-      <c r="M1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F4F88F6F7EE4CD4B82C1B33855E0F7E8" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="64cb4cc7036794b82b9e5aa8e91c3622">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399018e3-b857-408b-bd21-a6a80c979a4e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="94968af49f0175a612c20130cdc28d5d" ns2:_="">
     <xsd:import namespace="399018e3-b857-408b-bd21-a6a80c979a4e"/>
@@ -3245,6 +3353,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3255,22 +3369,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84FF387C-D0E4-41E3-A2B6-5759715EBA83}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="399018e3-b857-408b-bd21-a6a80c979a4e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{596B924E-C93B-4EBF-8185-7DC0083318E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3288,6 +3386,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84FF387C-D0E4-41E3-A2B6-5759715EBA83}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="399018e3-b857-408b-bd21-a6a80c979a4e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0374E2DF-FCF3-4A80-B78B-5197E355867A}">
   <ds:schemaRefs>

--- a/Plates/nitrate_key.xlsx
+++ b/Plates/nitrate_key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaedonswanson/Desktop/School/MS/Research/Microplate/Plates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9464C6-1B0C-1644-A740-946FD0B047EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E86D61-9077-3942-AA21-B315AB0F428F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="1" activeTab="5" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="8" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Format" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="72">
   <si>
     <t>A</t>
   </si>
@@ -142,13 +142,7 @@
     <t>gcp_05282026</t>
   </si>
   <si>
-    <t>JUST_REAGENT</t>
-  </si>
-  <si>
     <t>gcp_06122026</t>
-  </si>
-  <si>
-    <t>ERROR</t>
   </si>
   <si>
     <t>elm-bridge_06122026</t>
@@ -310,11 +304,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -702,13 +693,21 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -723,13 +722,21 @@
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -744,13 +751,21 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -765,13 +780,21 @@
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -786,13 +809,21 @@
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="E6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -807,13 +838,21 @@
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -828,13 +867,21 @@
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -849,13 +896,21 @@
       <c r="B9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="E9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -864,40 +919,6 @@
       <c r="M9" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -908,8 +929,11 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -957,23 +981,39 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="E2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="H2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="K2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="3" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -982,23 +1022,39 @@
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="H3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="I3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="K3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -1007,23 +1063,39 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="E4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="H4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="K4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1032,21 +1104,31 @@
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="H5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="I5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
@@ -1057,21 +1139,31 @@
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="E6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="H6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="I6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
@@ -1082,21 +1174,25 @@
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
@@ -1107,21 +1203,31 @@
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="E8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="H8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
@@ -1132,59 +1238,35 @@
       <c r="B9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="E9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="H9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1194,8 +1276,10 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -1243,18 +1327,30 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="E2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="H2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1266,13 +1362,21 @@
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -1287,13 +1391,21 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="E4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -1308,13 +1420,21 @@
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -1329,13 +1449,21 @@
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="E6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -1350,13 +1478,21 @@
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+        <v>37</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -1371,13 +1507,21 @@
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="E8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -1392,13 +1536,21 @@
       <c r="B9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="E9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -1407,40 +1559,6 @@
       <c r="M9" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1451,8 +1569,10 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="19.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -1500,23 +1620,39 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="E2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="L2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1525,23 +1661,39 @@
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E3" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="H3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="K3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -1550,23 +1702,39 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="E4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="H4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="K4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1575,23 +1743,39 @@
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="H5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="K5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -1600,23 +1784,39 @@
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="E6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="H6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="K6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -1625,23 +1825,39 @@
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="K7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -1650,23 +1866,39 @@
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="E8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="H8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="K8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -1675,59 +1907,41 @@
       <c r="B9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="E9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="H9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="K9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="L9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1786,245 +2000,245 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="E2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="L2" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="M2" t="s">
         <v>39</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>43</v>
+      <c r="E3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>44</v>
+      <c r="E4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>38</v>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>37</v>
+      <c r="E6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="2" t="s">
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" t="s">
         <v>30</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" t="s">
         <v>30</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2032,81 +2246,81 @@
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>32</v>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" t="s">
+        <v>31</v>
+      </c>
+      <c r="M8" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" s="2" t="s">
+      <c r="E9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="L9" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2170,263 +2384,230 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
+      <c r="H2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
+      <c r="H4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
+      <c r="E5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2440,7 +2621,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -2488,18 +2671,30 @@
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="E2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="H2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -2511,18 +2706,30 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="E3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="H3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="I3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -2534,18 +2741,30 @@
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="E4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="H4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -2557,18 +2776,30 @@
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="E5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="H5" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+        <v>66</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -2580,18 +2811,30 @@
       <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="H6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -2603,13 +2846,21 @@
       <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="E7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -2624,13 +2875,21 @@
       <c r="B8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="E8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -2645,13 +2904,21 @@
       <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -2660,40 +2927,6 @@
       <c r="M9" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2705,7 +2938,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -2753,18 +2988,30 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="E2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="H2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+        <v>65</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -2776,18 +3023,30 @@
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H3" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+        <v>64</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -2799,13 +3058,21 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="E4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+        <v>59</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2820,13 +3087,21 @@
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+        <v>60</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -2841,13 +3116,21 @@
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="E6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+        <v>70</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -2862,13 +3145,21 @@
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+        <v>61</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -2883,13 +3174,21 @@
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="E8" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+        <v>62</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -2904,13 +3203,21 @@
       <c r="B9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="E9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+        <v>63</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -2919,40 +3226,6 @@
       <c r="M9" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2964,6 +3237,8 @@
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -3011,18 +3286,30 @@
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="E2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="H2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+        <v>65</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -3034,18 +3321,30 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="E3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H3" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+        <v>64</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -3057,13 +3356,21 @@
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="E4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+        <v>59</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3078,13 +3385,21 @@
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="E5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+        <v>60</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -3099,13 +3414,21 @@
       <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+        <v>70</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -3120,13 +3443,21 @@
       <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="E7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+        <v>61</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -3141,13 +3472,21 @@
       <c r="B8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="E8" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+        <v>62</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -3162,13 +3501,21 @@
       <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="E9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+        <v>63</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -3177,40 +3524,6 @@
       <c r="M9" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3354,18 +3667,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3387,6 +3700,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0374E2DF-FCF3-4A80-B78B-5197E355867A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84FF387C-D0E4-41E3-A2B6-5759715EBA83}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -3400,12 +3721,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0374E2DF-FCF3-4A80-B78B-5197E355867A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Plates/nitrate_key.xlsx
+++ b/Plates/nitrate_key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaedonswanson/Desktop/School/MS/Research/Microplate/Plates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E86D61-9077-3942-AA21-B315AB0F428F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9455A1DE-7E34-E84C-BBF3-9AF5B4A02E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="8" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="2" activeTab="9" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Format" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="06192026_4" sheetId="9" r:id="rId7"/>
     <sheet name="06222026_1" sheetId="11" r:id="rId8"/>
     <sheet name="06222026_2" sheetId="12" r:id="rId9"/>
+    <sheet name="06242026_1" sheetId="13" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="76">
   <si>
     <t>A</t>
   </si>
@@ -263,6 +264,18 @@
   </si>
   <si>
     <t>elm-bridge_06012026</t>
+  </si>
+  <si>
+    <t>gcp-x5dilute_06212026</t>
+  </si>
+  <si>
+    <t>heron-resi-x5dilute_06212026</t>
+  </si>
+  <si>
+    <t>elm-school-x5dilute_06212026</t>
+  </si>
+  <si>
+    <t>heron-map-x5dilute_06212026</t>
   </si>
 </sst>
 </file>
@@ -304,9 +317,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -690,236 +702,423 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4611B2D-2CF4-9B4C-A279-90E2C6BCED9D}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="7" width="26.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -978,40 +1177,40 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>56</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" t="s">
         <v>56</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1019,40 +1218,40 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>54</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" t="s">
         <v>49</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1060,40 +1259,40 @@
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" t="s">
         <v>51</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" t="s">
         <v>51</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1101,170 +1300,152 @@
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>71</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>71</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>71</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" t="s">
         <v>66</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" t="s">
         <v>66</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" t="s">
         <v>66</v>
       </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1324,239 +1505,194 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1617,40 +1753,40 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1658,40 +1794,40 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>68</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" t="s">
         <v>41</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1699,40 +1835,40 @@
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>38</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1740,40 +1876,40 @@
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>44</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" t="s">
         <v>44</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1781,40 +1917,40 @@
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" t="s">
         <v>35</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1822,40 +1958,40 @@
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" t="s">
         <v>34</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" t="s">
         <v>30</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" t="s">
         <v>30</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1863,40 +1999,40 @@
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" t="s">
         <v>49</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" t="s">
         <v>49</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" t="s">
         <v>31</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1904,40 +2040,40 @@
       <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2668,263 +2804,230 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>52</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>53</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>53</v>
       </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>66</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
         <v>66</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>55</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" t="s">
         <v>55</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" t="s">
         <v>55</v>
       </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>56</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2985,245 +3088,203 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>65</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>65</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>64</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>64</v>
       </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>60</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>61</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>61</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>61</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>62</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>63</v>
       </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3232,7 +3293,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A762176-A398-AB4C-A136-6BF964D77C5A}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -3283,245 +3344,251 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>65</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>65</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>64</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>64</v>
       </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>60</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>61</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>61</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>61</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>62</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>63</v>
       </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11">
+        <v>2.7320000000000002</v>
+      </c>
+      <c r="G11">
+        <f>F11/5</f>
+        <v>0.5464</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12">
+        <v>1.012</v>
+      </c>
+      <c r="G12">
+        <f t="shared" ref="G12:G14" si="0">F12/5</f>
+        <v>0.2024</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>0.1978</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14">
+        <v>1.599</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>0.31979999999999997</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3529,6 +3596,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F4F88F6F7EE4CD4B82C1B33855E0F7E8" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="64cb4cc7036794b82b9e5aa8e91c3622">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399018e3-b857-408b-bd21-a6a80c979a4e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="94968af49f0175a612c20130cdc28d5d" ns2:_="">
     <xsd:import namespace="399018e3-b857-408b-bd21-a6a80c979a4e"/>
@@ -3666,15 +3742,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -3682,6 +3749,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0374E2DF-FCF3-4A80-B78B-5197E355867A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{596B924E-C93B-4EBF-8185-7DC0083318E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3695,14 +3770,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0374E2DF-FCF3-4A80-B78B-5197E355867A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Plates/nitrate_key.xlsx
+++ b/Plates/nitrate_key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaedonswanson/Desktop/School/MS/Research/Microplate/Plates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9455A1DE-7E34-E84C-BBF3-9AF5B4A02E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0487EB1C-5029-9441-9D0A-8398755B4365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="2" activeTab="9" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="2" activeTab="10" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Format" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="06222026_1" sheetId="11" r:id="rId8"/>
     <sheet name="06222026_2" sheetId="12" r:id="rId9"/>
     <sheet name="06242026_1" sheetId="13" r:id="rId10"/>
+    <sheet name="06242026_2" sheetId="14" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="76">
   <si>
     <t>A</t>
   </si>
@@ -1123,6 +1124,241 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE356DF9-3DB6-A147-886E-7F10FC68241C}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="7" width="26.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A228D01-3A45-7E46-912C-9944342FCD5A}">
   <dimension ref="A1:M9"/>

--- a/Plates/nitrate_key.xlsx
+++ b/Plates/nitrate_key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaedonswanson/Desktop/School/MS/Research/Microplate/Plates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0487EB1C-5029-9441-9D0A-8398755B4365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D34686-64EB-4148-86A4-85FB9D313436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="2" activeTab="10" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="2" activeTab="8" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Format" sheetId="1" r:id="rId1"/>
@@ -22,8 +22,6 @@
     <sheet name="06192026_4" sheetId="9" r:id="rId7"/>
     <sheet name="06222026_1" sheetId="11" r:id="rId8"/>
     <sheet name="06222026_2" sheetId="12" r:id="rId9"/>
-    <sheet name="06242026_1" sheetId="13" r:id="rId10"/>
-    <sheet name="06242026_2" sheetId="14" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -49,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="72">
   <si>
     <t>A</t>
   </si>
@@ -265,18 +263,6 @@
   </si>
   <si>
     <t>elm-bridge_06012026</t>
-  </si>
-  <si>
-    <t>gcp-x5dilute_06212026</t>
-  </si>
-  <si>
-    <t>heron-resi-x5dilute_06212026</t>
-  </si>
-  <si>
-    <t>elm-school-x5dilute_06212026</t>
-  </si>
-  <si>
-    <t>heron-map-x5dilute_06212026</t>
   </si>
 </sst>
 </file>
@@ -889,476 +875,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4611B2D-2CF4-9B4C-A279-90E2C6BCED9D}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="5" max="7" width="26.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B1">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <v>2</v>
-      </c>
-      <c r="D1">
-        <v>3</v>
-      </c>
-      <c r="E1">
-        <v>4</v>
-      </c>
-      <c r="F1">
-        <v>5</v>
-      </c>
-      <c r="G1">
-        <v>6</v>
-      </c>
-      <c r="H1">
-        <v>7</v>
-      </c>
-      <c r="I1">
-        <v>8</v>
-      </c>
-      <c r="J1">
-        <v>9</v>
-      </c>
-      <c r="K1">
-        <v>10</v>
-      </c>
-      <c r="L1">
-        <v>11</v>
-      </c>
-      <c r="M1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE356DF9-3DB6-A147-886E-7F10FC68241C}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="5" max="7" width="26.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B1">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <v>2</v>
-      </c>
-      <c r="D1">
-        <v>3</v>
-      </c>
-      <c r="E1">
-        <v>4</v>
-      </c>
-      <c r="F1">
-        <v>5</v>
-      </c>
-      <c r="G1">
-        <v>6</v>
-      </c>
-      <c r="H1">
-        <v>7</v>
-      </c>
-      <c r="I1">
-        <v>8</v>
-      </c>
-      <c r="J1">
-        <v>9</v>
-      </c>
-      <c r="K1">
-        <v>10</v>
-      </c>
-      <c r="L1">
-        <v>11</v>
-      </c>
-      <c r="M1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A228D01-3A45-7E46-912C-9944342FCD5A}">
   <dimension ref="A1:M9"/>
@@ -3529,13 +3045,14 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A762176-A398-AB4C-A136-6BF964D77C5A}">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="3.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -3776,54 +3293,6 @@
       </c>
       <c r="G9" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11">
-        <v>2.7320000000000002</v>
-      </c>
-      <c r="G11">
-        <f>F11/5</f>
-        <v>0.5464</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12">
-        <v>1.012</v>
-      </c>
-      <c r="G12">
-        <f t="shared" ref="G12:G14" si="0">F12/5</f>
-        <v>0.2024</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13">
-        <v>0.98899999999999999</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="0"/>
-        <v>0.1978</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14">
-        <v>1.599</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>0.31979999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -3832,12 +3301,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3979,15 +3445,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0374E2DF-FCF3-4A80-B78B-5197E355867A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84FF387C-D0E4-41E3-A2B6-5759715EBA83}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="399018e3-b857-408b-bd21-a6a80c979a4e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4011,17 +3488,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84FF387C-D0E4-41E3-A2B6-5759715EBA83}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0374E2DF-FCF3-4A80-B78B-5197E355867A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="399018e3-b857-408b-bd21-a6a80c979a4e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Plates/nitrate_key.xlsx
+++ b/Plates/nitrate_key.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaedonswanson/Desktop/School/MS/Research/Microplate/Plates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D34686-64EB-4148-86A4-85FB9D313436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9E35AD-FE2E-D34E-B0F5-235A9D721438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="2" activeTab="8" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="9" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Format" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="06192026_4" sheetId="9" r:id="rId7"/>
     <sheet name="06222026_1" sheetId="11" r:id="rId8"/>
     <sheet name="06222026_2" sheetId="12" r:id="rId9"/>
+    <sheet name="06252026_1" sheetId="13" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="76">
   <si>
     <t>A</t>
   </si>
@@ -263,6 +264,18 @@
   </si>
   <si>
     <t>elm-bridge_06012026</t>
+  </si>
+  <si>
+    <t>heron-map-x5dilute_06212026</t>
+  </si>
+  <si>
+    <t>heron-resi-x5dilute_06212026</t>
+  </si>
+  <si>
+    <t>elm-school-x5dilute_06212026</t>
+  </si>
+  <si>
+    <t>gcp-x5dilute_06212026</t>
   </si>
 </sst>
 </file>
@@ -640,6 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2537F3F9-8DB7-D542-9661-67B70C299690}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -875,8 +889,248 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA6069E-56EC-874E-8138-0C9F9F6F6420}">
+  <sheetPr codeName="Sheet10"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="26.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A228D01-3A45-7E46-912C-9944342FCD5A}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1206,6 +1460,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55F4A5C2-CC37-4DE5-8D3C-DCD54EC66921}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1454,6 +1709,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F440DE84-DF99-4AAA-815E-10A80CB578E0}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1837,6 +2093,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{789EDA15-6520-4C56-8C16-6BF2362B08F7}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2220,6 +2477,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9D2C9A-CA68-4C73-8E9C-B2F3F39F8518}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2505,6 +2763,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9A2FE2-4864-4798-9335-55F3D4E7525C}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2789,6 +3048,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF55D13E-4202-B24E-90AB-F581E60463A8}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3045,6 +3305,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A762176-A398-AB4C-A136-6BF964D77C5A}">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3301,9 +3562,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3445,26 +3709,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84FF387C-D0E4-41E3-A2B6-5759715EBA83}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0374E2DF-FCF3-4A80-B78B-5197E355867A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="399018e3-b857-408b-bd21-a6a80c979a4e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3488,9 +3741,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0374E2DF-FCF3-4A80-B78B-5197E355867A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84FF387C-D0E4-41E3-A2B6-5759715EBA83}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="399018e3-b857-408b-bd21-a6a80c979a4e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Plates/nitrate_key.xlsx
+++ b/Plates/nitrate_key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaedonswanson/Desktop/School/MS/Research/Microplate/Plates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9E35AD-FE2E-D34E-B0F5-235A9D721438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A549F20-AEC2-7D47-BC75-46C427D1F3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="9" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="5" activeTab="11" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Format" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,8 @@
     <sheet name="06222026_1" sheetId="11" r:id="rId8"/>
     <sheet name="06222026_2" sheetId="12" r:id="rId9"/>
     <sheet name="06252026_1" sheetId="13" r:id="rId10"/>
+    <sheet name="08032026_1" sheetId="14" r:id="rId11"/>
+    <sheet name="08032026_2" sheetId="15" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="102">
   <si>
     <t>A</t>
   </si>
@@ -276,13 +278,91 @@
   </si>
   <si>
     <t>gcp-x5dilute_06212026</t>
+  </si>
+  <si>
+    <t>gcp_07312026</t>
+  </si>
+  <si>
+    <t>gcp-x5dilute_07312026</t>
+  </si>
+  <si>
+    <t>elm-bridge_07312026</t>
+  </si>
+  <si>
+    <t>elm-bridge-x5dilute_07312026</t>
+  </si>
+  <si>
+    <t>elm-school-x5dilute_07312026</t>
+  </si>
+  <si>
+    <t>elm-school_07312026</t>
+  </si>
+  <si>
+    <t>adams-in_07312026</t>
+  </si>
+  <si>
+    <t>adams-in-x5dilute_07312026</t>
+  </si>
+  <si>
+    <t>adams-mid-up_07312026</t>
+  </si>
+  <si>
+    <t>adams-mid-up-x5dilute_07312026</t>
+  </si>
+  <si>
+    <t>adams-mid-down_07312026</t>
+  </si>
+  <si>
+    <t>adams-mid-down-x5dilute_07312026</t>
+  </si>
+  <si>
+    <t>adams-out_07312026</t>
+  </si>
+  <si>
+    <t>adams-out-x5dilute_07312026</t>
+  </si>
+  <si>
+    <t>heron-resi_07312026</t>
+  </si>
+  <si>
+    <t>heron-resi-x5dilute_07312026</t>
+  </si>
+  <si>
+    <t>heron-map_07312026</t>
+  </si>
+  <si>
+    <t>heron-map-x5dilute_07312026</t>
+  </si>
+  <si>
+    <t>heron-out_07312026</t>
+  </si>
+  <si>
+    <t>heron-out-x5dilute_07312026</t>
+  </si>
+  <si>
+    <t>adams-mid-up-x5dilute_06212026</t>
+  </si>
+  <si>
+    <t>elm-bridge-x5dilute_06212026</t>
+  </si>
+  <si>
+    <t>adams-mid-down-x5dilute_06212026</t>
+  </si>
+  <si>
+    <t>heron-out-x5dilute_06212026</t>
+  </si>
+  <si>
+    <t>adams-out-x5dilute_06212026</t>
+  </si>
+  <si>
+    <t>adams-in-x5dilute_06212026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -292,6 +372,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -317,8 +404,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1128,6 +1216,709 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EDA6053-DCFD-7540-B637-C50E77A74717}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="7" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="26.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BAA4F88-CB06-5846-8EA7-11FE4439FF5B}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="7" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="26.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A228D01-3A45-7E46-912C-9944342FCD5A}">
   <sheetPr codeName="Sheet2"/>
@@ -3562,6 +4353,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3570,7 +4367,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F4F88F6F7EE4CD4B82C1B33855E0F7E8" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="64cb4cc7036794b82b9e5aa8e91c3622">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399018e3-b857-408b-bd21-a6a80c979a4e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="94968af49f0175a612c20130cdc28d5d" ns2:_="">
     <xsd:import namespace="399018e3-b857-408b-bd21-a6a80c979a4e"/>
@@ -3708,13 +4505,23 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84FF387C-D0E4-41E3-A2B6-5759715EBA83}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="399018e3-b857-408b-bd21-a6a80c979a4e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0374E2DF-FCF3-4A80-B78B-5197E355867A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -3722,7 +4529,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{596B924E-C93B-4EBF-8185-7DC0083318E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3738,20 +4545,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84FF387C-D0E4-41E3-A2B6-5759715EBA83}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="399018e3-b857-408b-bd21-a6a80c979a4e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Plates/nitrate_key.xlsx
+++ b/Plates/nitrate_key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaedonswanson/Desktop/School/MS/Research/Microplate/Plates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A549F20-AEC2-7D47-BC75-46C427D1F3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F776B26-CCC0-F44B-9876-F1893190C44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="5" activeTab="11" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="6" activeTab="9" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Format" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="103">
   <si>
     <t>A</t>
   </si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t>adams-in-x5dilute_06212026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -980,7 +983,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA6069E-56EC-874E-8138-0C9F9F6F6420}">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -1209,6 +1212,11 @@
       </c>
       <c r="G9" t="s">
         <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="H16" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Plates/nitrate_key.xlsx
+++ b/Plates/nitrate_key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaedonswanson/Desktop/School/MS/Research/Microplate/Plates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F776B26-CCC0-F44B-9876-F1893190C44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A241B73-52F7-054D-BAD8-5A41C377B2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="6" activeTab="9" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="6" activeTab="12" xr2:uid="{B6428683-2A57-0F44-B42C-96122C72F6E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Format" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="06252026_1" sheetId="13" r:id="rId10"/>
     <sheet name="08032026_1" sheetId="14" r:id="rId11"/>
     <sheet name="08032026_2" sheetId="15" r:id="rId12"/>
+    <sheet name="08052026_1" sheetId="16" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="123">
   <si>
     <t>A</t>
   </si>
@@ -359,6 +360,66 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>gcp_08052026</t>
+  </si>
+  <si>
+    <t>adams-mid-up_08052026</t>
+  </si>
+  <si>
+    <t>heron-map_08052026</t>
+  </si>
+  <si>
+    <t>gcp-x5dilute_08052026</t>
+  </si>
+  <si>
+    <t>adams-mid-up-x5dilute_08052026</t>
+  </si>
+  <si>
+    <t>heron-map-x5dilute_08052026</t>
+  </si>
+  <si>
+    <t>elm-bridge_08052026</t>
+  </si>
+  <si>
+    <t>adams-mid-down_08052026</t>
+  </si>
+  <si>
+    <t>heron-out_08052026</t>
+  </si>
+  <si>
+    <t>elm-bridge-x5dilute_08052026</t>
+  </si>
+  <si>
+    <t>adams-mid-down-x5dilute_08052026</t>
+  </si>
+  <si>
+    <t>heron-out-x5dilute_08052026</t>
+  </si>
+  <si>
+    <t>elm-school_08052026</t>
+  </si>
+  <si>
+    <t>adams-out_08052026</t>
+  </si>
+  <si>
+    <t>elm-school-x5dilute_08052026</t>
+  </si>
+  <si>
+    <t>adams-out-x5dilute_08052026</t>
+  </si>
+  <si>
+    <t>adams-in_08052026</t>
+  </si>
+  <si>
+    <t>heron-resi_08052026</t>
+  </si>
+  <si>
+    <t>adams-in-x5dilute_08052026</t>
+  </si>
+  <si>
+    <t>heron-resi-x5dilute_08052026</t>
   </si>
 </sst>
 </file>
@@ -1927,6 +1988,351 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9D69B8D-BD0D-B74C-AE55-5563714112C3}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="7" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="26.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G5" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G7" t="s">
+        <v>117</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A228D01-3A45-7E46-912C-9944342FCD5A}">
   <sheetPr codeName="Sheet2"/>
@@ -4361,21 +4767,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F4F88F6F7EE4CD4B82C1B33855E0F7E8" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="64cb4cc7036794b82b9e5aa8e91c3622">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="399018e3-b857-408b-bd21-a6a80c979a4e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="94968af49f0175a612c20130cdc28d5d" ns2:_="">
     <xsd:import namespace="399018e3-b857-408b-bd21-a6a80c979a4e"/>
@@ -4513,31 +4904,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84FF387C-D0E4-41E3-A2B6-5759715EBA83}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="399018e3-b857-408b-bd21-a6a80c979a4e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0374E2DF-FCF3-4A80-B78B-5197E355867A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{596B924E-C93B-4EBF-8185-7DC0083318E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4553,4 +4935,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0374E2DF-FCF3-4A80-B78B-5197E355867A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84FF387C-D0E4-41E3-A2B6-5759715EBA83}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="399018e3-b857-408b-bd21-a6a80c979a4e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>